--- a/EXCEL/Exercise Files/Chapter05/05_05_SingleCorrelation.xlsx
+++ b/EXCEL/Exercise Files/Chapter05/05_05_SingleCorrelation.xlsx
@@ -1,24 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Storage 2\Writing\Lynda\Data Analysis Fundamentals 20220331 Refresh\Exercise Files\Chapter05\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8116D3-633C-4E80-BF73-0D6F4C368644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46D395B-3805-49EE-B66A-9E3A4B47AC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25830" yWindow="15" windowWidth="25830" windowHeight="21540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="288" yWindow="324" windowWidth="22752" windowHeight="11916" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -364,12 +373,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:D12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -380,84 +389,124 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <f>CORREL(A3:A12,B3:B12)</f>
+        <v>0.69488489447433488</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>4</v>
       </c>
       <c r="B4">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <f t="shared" ref="D4:D12" si="0">CORREL(A4:A13,B4:B13)</f>
+        <v>0.64117946872237808</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>7</v>
       </c>
       <c r="B5">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>0.69278000435065834</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2</v>
       </c>
       <c r="B6">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>0.67157769306378923</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3</v>
       </c>
       <c r="B7">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>0.58298476444549541</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>0.4789090502210136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>0.56693405487706339</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>0.78571428571428559</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>6</v>
       </c>
       <c r="B11">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12">
         <v>18</v>
+      </c>
+      <c r="D12" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
